--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484166_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484166_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4689</v>
+        <v>4.7291</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9249</v>
+        <v>5.129</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.456</v>
+        <v>-0.3999</v>
       </c>
       <c r="G2" t="n">
         <v>3.2384</v>
@@ -610,13 +610,13 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.297</v>
+        <v>-0.0368</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.059</v>
+        <v>-0.0029</v>
       </c>
       <c r="V2" t="n">
         <v>0.3373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7892</v>
+        <v>2.2799</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0445</v>
+        <v>1.6193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7448</v>
+        <v>0.6606</v>
       </c>
       <c r="G3" t="n">
         <v>0.2968</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0832</v>
+        <v>0.5739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7483</v>
+        <v>0.3231</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3349</v>
+        <v>0.2507</v>
       </c>
       <c r="V3" t="n">
         <v>2.0044</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6171</v>
+        <v>1.3562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4783</v>
+        <v>1.4419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1388</v>
+        <v>-0.0857</v>
       </c>
       <c r="G4" t="n">
         <v>3.1927</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3934</v>
+        <v>0.3457</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7141</v>
+        <v>0.2495</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3207</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3162</v>
+        <v>0.5632</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1208</v>
+        <v>1.275</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1954</v>
+        <v>-0.7118</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1978</v>
+        <v>-0.7929</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1511</v>
+        <v>-1.2451</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0467</v>
+        <v>0.4522</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1208</v>
+        <v>1.4563</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0806</v>
+        <v>1.2956</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0.1606</v>
       </c>
       <c r="M5" t="n">
-        <v>0.077</v>
+        <v>-2.2492</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07049999999999999</v>
+        <v>-2.5408</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0065</v>
+        <v>0.2916</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0799</v>
+        <v>-0.3698</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.1813</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0799</v>
+        <v>-0.1885</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.292</v>
+        <v>0.5024</v>
       </c>
       <c r="E6" t="n">
-        <v>1.088</v>
+        <v>0.2228</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.796</v>
+        <v>0.2796</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7929</v>
+        <v>0.1978</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2451</v>
+        <v>0.1511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4522</v>
+        <v>0.0467</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4563</v>
+        <v>0.1208</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2956</v>
+        <v>0.0806</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1606</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2492</v>
+        <v>0.077</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5408</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2916</v>
+        <v>0.0065</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.641</v>
+        <v>0.1063</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3683</v>
+        <v>0.102</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2727</v>
+        <v>0.0042</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8174</v>
+        <v>-0.8953</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6869</v>
+        <v>1.7493</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5043</v>
+        <v>-2.6446</v>
       </c>
       <c r="G7" t="n">
         <v>-0.09229999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3542</v>
+        <v>0.2763</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3288</v>
+        <v>0.3912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0254</v>
+        <v>-0.1149</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2777</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8929</v>
+        <v>-1.4684</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1789</v>
+        <v>0.5473</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0718</v>
+        <v>-2.0157</v>
       </c>
       <c r="G8" t="n">
         <v>-0.09909999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0679</v>
+        <v>-0.6433</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7368</v>
+        <v>-0.3684</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3311</v>
+        <v>-0.275</v>
       </c>
       <c r="V8" t="n">
         <v>0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.948</v>
+        <v>-4.8523</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6843</v>
+        <v>0.8081</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.6323</v>
+        <v>-5.6604</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8437</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1183</v>
+        <v>0.214</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7379</v>
+        <v>0.8617</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6196</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4129</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.758599999999999</v>
+        <v>-7.9751</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3403</v>
+        <v>-3.7148</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4183</v>
+        <v>-4.2603</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.1895</v>
+        <v>-6.0053</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4234</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.766</v>
+        <v>-5.1681</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8829</v>
+        <v>-2.5643</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1124</v>
+        <v>1.4315</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9953</v>
+        <v>-3.9957</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3066</v>
+        <v>-3.441</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5359</v>
+        <v>-2.2687</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.1723</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.9536</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4817</v>
+        <v>-0.1586</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.795</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8097</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.3992</v>
+        <v>-8.3255</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.718</v>
+        <v>-4.6828</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6812</v>
+        <v>-3.6427</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0053</v>
+        <v>-5.1895</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-2.4234</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.1681</v>
+        <v>-2.766</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5643</v>
+        <v>-1.8829</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4315</v>
+        <v>0.1124</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.9957</v>
+        <v>-1.9953</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.441</v>
+        <v>-3.3066</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2687</v>
+        <v>-2.5359</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1723</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
         <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3777</v>
+        <v>-0.136</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1619</v>
+        <v>0.1758</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2159</v>
+        <v>-0.3119</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8097</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.3327</v>
+        <v>-14.0858</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1483</v>
+        <v>4.395099999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-18.4809</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.097100000000001</v>
+        <v>-9.097099999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.0564</v>
+        <v>-7.056400000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-2.040400000000001</v>
@@ -1366,10 +1366,10 @@
         <v>11.0509</v>
       </c>
       <c r="K12" t="n">
-        <v>8.6225</v>
+        <v>8.622499999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.428399999999999</v>
+        <v>2.4284</v>
       </c>
       <c r="M12" t="n">
         <v>-20.148</v>
@@ -1381,7 +1381,7 @@
         <v>-4.4687</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.8949</v>
@@ -1390,13 +1390,13 @@
         <v>12.8951</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8703</v>
+        <v>-0.6233000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1141999999999996</v>
+        <v>1.361</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9846</v>
+        <v>-1.9848</v>
       </c>
       <c r="V12" t="n">
         <v>-4.365</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5713</v>
+        <v>6.9149</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2484</v>
+        <v>5.4322</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3229</v>
+        <v>1.4827</v>
       </c>
       <c r="G13" t="n">
         <v>3.6456</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>1.858</v>
+        <v>1.2017</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5532</v>
+        <v>0.7369</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3049</v>
+        <v>0.4647</v>
       </c>
       <c r="V13" t="n">
         <v>1.4724</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0415</v>
+        <v>4.5723</v>
       </c>
       <c r="E14" t="n">
-        <v>2.615</v>
+        <v>2.4109</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4265</v>
+        <v>2.1613</v>
       </c>
       <c r="G14" t="n">
         <v>2.046</v>
@@ -1546,13 +1546,13 @@
         <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0903</v>
+        <v>1.621</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5726</v>
+        <v>0.3685</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5177</v>
+        <v>1.2525</v>
       </c>
       <c r="V14" t="n">
         <v>3.0874</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2621</v>
+        <v>3.2628</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8669</v>
+        <v>4.4791</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6048</v>
+        <v>-1.2163</v>
       </c>
       <c r="G15" t="n">
         <v>4.8282</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1694</v>
+        <v>-0.1686</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4137</v>
+        <v>0.1985</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7556</v>
+        <v>-0.3671</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6292</v>
+        <v>2.0033</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2339</v>
+        <v>1.3359</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3953</v>
+        <v>0.6674</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2834</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0396</v>
+        <v>0.4138</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1418</v>
+        <v>0.2438</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1021</v>
+        <v>0.1699</v>
       </c>
       <c r="V16" t="n">
         <v>2.4842</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9129</v>
+        <v>1.9092</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5668</v>
+        <v>1.9494</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6539</v>
+        <v>-0.0403</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7854</v>
+        <v>0.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8829</v>
+        <v>1.295</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0975</v>
+        <v>-1.245</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3036</v>
+        <v>1.9355</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9436</v>
+        <v>3.09</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.64</v>
+        <v>-1.1545</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5181</v>
+        <v>-1.8855</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0607</v>
+        <v>-1.795</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4574</v>
+        <v>-0.0905</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>0.195</v>
+        <v>0.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2551</v>
+        <v>0.4026</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0601</v>
+        <v>0.1274</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X17" t="n">
         <v>-0.266</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5193</v>
+        <v>0.9673</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2947</v>
+        <v>1.2607</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2245</v>
+        <v>-0.2934</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6227</v>
+        <v>0.7854</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3582</v>
+        <v>2.8829</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2645</v>
+        <v>-2.0975</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5951</v>
+        <v>2.3036</v>
       </c>
       <c r="K18" t="n">
-        <v>0.555</v>
+        <v>2.9436</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>-0.64</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0276</v>
+        <v>-1.5181</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1967</v>
+        <v>-0.0607</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2244</v>
+        <v>-1.4574</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2262</v>
+        <v>0.2494</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3004</v>
+        <v>-0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0742</v>
+        <v>0.3004</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5097</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4393</v>
+        <v>0.2947</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9295</v>
+        <v>0.2764</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05</v>
+        <v>1.6227</v>
       </c>
       <c r="H19" t="n">
-        <v>1.295</v>
+        <v>0.3582</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.245</v>
+        <v>1.2645</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9355</v>
+        <v>0.5951</v>
       </c>
       <c r="K19" t="n">
-        <v>3.09</v>
+        <v>0.555</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1545</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8855</v>
+        <v>1.0276</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.795</v>
+        <v>-0.1967</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0905</v>
+        <v>1.2244</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.1743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1076</v>
+        <v>-0.3004</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7619</v>
+        <v>0.1261</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3373</v>
+        <v>-1.4724</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5524</v>
+        <v>-1.3951</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6542</v>
+        <v>-1.3481</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1018</v>
+        <v>-0.047</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6601</v>
@@ -2014,13 +2014,13 @@
         <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2465</v>
+        <v>0.4038</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1076</v>
+        <v>0.1985</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3541</v>
+        <v>0.2053</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3373</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5608</v>
+        <v>-1.4324</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8701</v>
+        <v>2.666</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4309</v>
+        <v>-4.0985</v>
       </c>
       <c r="G21" t="n">
         <v>0.0625</v>
@@ -2092,13 +2092,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2941</v>
+        <v>-0.1658</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3912</v>
+        <v>0.1871</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6853</v>
+        <v>-0.3529</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3373</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.3328</v>
+        <v>17.3734</v>
       </c>
       <c r="E22" t="n">
-        <v>18.4809</v>
+        <v>18.4808</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.148100000000001</v>
+        <v>-1.107699999999999</v>
       </c>
       <c r="G22" t="n">
         <v>9.0969</v>
       </c>
       <c r="H22" t="n">
-        <v>7.0564</v>
+        <v>7.056399999999999</v>
       </c>
       <c r="I22" t="n">
         <v>2.0405</v>
@@ -2170,13 +2170,13 @@
         <v>12.895</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8702</v>
+        <v>3.911</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9846</v>
+        <v>1.9845</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1141000000000001</v>
+        <v>1.9263</v>
       </c>
       <c r="V22" t="n">
         <v>4.365100000000001</v>
